--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/VIRGINIA_2019.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/VIRGINIA_2019.xlsx
@@ -535,7 +535,7 @@
         <v>5</v>
       </c>
       <c r="D10">
-        <v>0.0009428625306430323</v>
+        <v>0.0009428625306430324</v>
       </c>
     </row>
     <row r="11">
@@ -553,7 +553,7 @@
         <v>5</v>
       </c>
       <c r="D11">
-        <v>0.0009428625306430323</v>
+        <v>0.0009428625306430324</v>
       </c>
     </row>
     <row r="12">
@@ -823,7 +823,7 @@
         <v>5</v>
       </c>
       <c r="D26">
-        <v>0.0009428625306430323</v>
+        <v>0.0009428625306430324</v>
       </c>
     </row>
     <row r="27">
@@ -1579,7 +1579,7 @@
         <v>5</v>
       </c>
       <c r="D68">
-        <v>0.0009428625306430323</v>
+        <v>0.0009428625306430324</v>
       </c>
     </row>
     <row r="69">
@@ -2353,7 +2353,7 @@
         <v>5</v>
       </c>
       <c r="D111">
-        <v>0.0009428625306430323</v>
+        <v>0.0009428625306430324</v>
       </c>
     </row>
     <row r="112">
@@ -2731,7 +2731,7 @@
         <v>5</v>
       </c>
       <c r="D132">
-        <v>0.0009428625306430323</v>
+        <v>0.0009428625306430324</v>
       </c>
     </row>
     <row r="133">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C214">
@@ -4513,7 +4513,7 @@
         <v>5</v>
       </c>
       <c r="D231">
-        <v>0.0009428625306430323</v>
+        <v>0.0009428625306430324</v>
       </c>
     </row>
     <row r="232">
@@ -4549,7 +4549,7 @@
         <v>5</v>
       </c>
       <c r="D233">
-        <v>0.0009428625306430323</v>
+        <v>0.0009428625306430324</v>
       </c>
     </row>
     <row r="234">
@@ -4855,7 +4855,7 @@
         <v>5</v>
       </c>
       <c r="D250">
-        <v>0.0009428625306430323</v>
+        <v>0.0009428625306430324</v>
       </c>
     </row>
     <row r="251">
@@ -5143,7 +5143,7 @@
         <v>5</v>
       </c>
       <c r="D266">
-        <v>0.0009428625306430323</v>
+        <v>0.0009428625306430324</v>
       </c>
     </row>
     <row r="267">
@@ -5251,7 +5251,7 @@
         <v>5</v>
       </c>
       <c r="D272">
-        <v>0.0009428625306430323</v>
+        <v>0.0009428625306430324</v>
       </c>
     </row>
     <row r="273">
@@ -5593,7 +5593,7 @@
         <v>5</v>
       </c>
       <c r="D291">
-        <v>0.0009428625306430323</v>
+        <v>0.0009428625306430324</v>
       </c>
     </row>
     <row r="292">
@@ -5647,7 +5647,7 @@
         <v>5</v>
       </c>
       <c r="D294">
-        <v>0.0009428625306430323</v>
+        <v>0.0009428625306430324</v>
       </c>
     </row>
     <row r="295">
@@ -6169,7 +6169,7 @@
         <v>5</v>
       </c>
       <c r="D323">
-        <v>0.0009428625306430323</v>
+        <v>0.0009428625306430324</v>
       </c>
     </row>
     <row r="324">
@@ -6295,7 +6295,7 @@
         <v>5</v>
       </c>
       <c r="D330">
-        <v>0.0009428625306430323</v>
+        <v>0.0009428625306430324</v>
       </c>
     </row>
     <row r="331">
@@ -6331,7 +6331,7 @@
         <v>52</v>
       </c>
       <c r="D332">
-        <v>0.009805770318687535</v>
+        <v>0.009805770318687537</v>
       </c>
     </row>
     <row r="333">
@@ -7087,7 +7087,7 @@
         <v>5</v>
       </c>
       <c r="D374">
-        <v>0.0009428625306430323</v>
+        <v>0.0009428625306430324</v>
       </c>
     </row>
     <row r="375">
@@ -7429,7 +7429,7 @@
         <v>5</v>
       </c>
       <c r="D393">
-        <v>0.0009428625306430323</v>
+        <v>0.0009428625306430324</v>
       </c>
     </row>
     <row r="394">
@@ -7933,7 +7933,7 @@
         <v>5</v>
       </c>
       <c r="D421">
-        <v>0.0009428625306430323</v>
+        <v>0.0009428625306430324</v>
       </c>
     </row>
     <row r="422">
@@ -8743,7 +8743,7 @@
         <v>5</v>
       </c>
       <c r="D466">
-        <v>0.0009428625306430323</v>
+        <v>0.0009428625306430324</v>
       </c>
     </row>
     <row r="467">
@@ -8761,7 +8761,7 @@
         <v>5</v>
       </c>
       <c r="D467">
-        <v>0.0009428625306430323</v>
+        <v>0.0009428625306430324</v>
       </c>
     </row>
     <row r="468">
@@ -8797,7 +8797,7 @@
         <v>5</v>
       </c>
       <c r="D469">
-        <v>0.0009428625306430323</v>
+        <v>0.0009428625306430324</v>
       </c>
     </row>
     <row r="470">
@@ -9103,7 +9103,7 @@
         <v>5</v>
       </c>
       <c r="D486">
-        <v>0.0009428625306430323</v>
+        <v>0.0009428625306430324</v>
       </c>
     </row>
     <row r="487">
@@ -9193,7 +9193,7 @@
         <v>5</v>
       </c>
       <c r="D491">
-        <v>0.0009428625306430323</v>
+        <v>0.0009428625306430324</v>
       </c>
     </row>
     <row r="492">
@@ -9265,7 +9265,7 @@
         <v>5</v>
       </c>
       <c r="D495">
-        <v>0.0009428625306430323</v>
+        <v>0.0009428625306430324</v>
       </c>
     </row>
     <row r="496">
@@ -9301,7 +9301,7 @@
         <v>5</v>
       </c>
       <c r="D497">
-        <v>0.0009428625306430323</v>
+        <v>0.0009428625306430324</v>
       </c>
     </row>
     <row r="498">
@@ -9535,7 +9535,7 @@
         <v>5</v>
       </c>
       <c r="D510">
-        <v>0.0009428625306430323</v>
+        <v>0.0009428625306430324</v>
       </c>
     </row>
     <row r="511">
@@ -9607,7 +9607,7 @@
         <v>5</v>
       </c>
       <c r="D514">
-        <v>0.0009428625306430323</v>
+        <v>0.0009428625306430324</v>
       </c>
     </row>
     <row r="515">
@@ -10680,7 +10680,7 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C574">
@@ -11130,7 +11130,7 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C599">
@@ -12037,7 +12037,7 @@
         <v>5</v>
       </c>
       <c r="D649">
-        <v>0.0009428625306430323</v>
+        <v>0.0009428625306430324</v>
       </c>
     </row>
     <row r="650">
@@ -12631,7 +12631,7 @@
         <v>5</v>
       </c>
       <c r="D682">
-        <v>0.0009428625306430323</v>
+        <v>0.0009428625306430324</v>
       </c>
     </row>
     <row r="683">
@@ -12775,7 +12775,7 @@
         <v>5</v>
       </c>
       <c r="D690">
-        <v>0.0009428625306430323</v>
+        <v>0.0009428625306430324</v>
       </c>
     </row>
     <row r="691">
@@ -12919,7 +12919,7 @@
         <v>5</v>
       </c>
       <c r="D698">
-        <v>0.0009428625306430323</v>
+        <v>0.0009428625306430324</v>
       </c>
     </row>
     <row r="699">
@@ -13045,7 +13045,7 @@
         <v>5</v>
       </c>
       <c r="D705">
-        <v>0.0009428625306430323</v>
+        <v>0.0009428625306430324</v>
       </c>
     </row>
     <row r="706">
@@ -13693,7 +13693,7 @@
         <v>5</v>
       </c>
       <c r="D741">
-        <v>0.0009428625306430323</v>
+        <v>0.0009428625306430324</v>
       </c>
     </row>
     <row r="742">
@@ -13837,7 +13837,7 @@
         <v>5</v>
       </c>
       <c r="D749">
-        <v>0.0009428625306430323</v>
+        <v>0.0009428625306430324</v>
       </c>
     </row>
     <row r="750">
@@ -14485,7 +14485,7 @@
         <v>5</v>
       </c>
       <c r="D785">
-        <v>0.0009428625306430323</v>
+        <v>0.0009428625306430324</v>
       </c>
     </row>
     <row r="786">
@@ -14917,7 +14917,7 @@
         <v>5</v>
       </c>
       <c r="D809">
-        <v>0.0009428625306430323</v>
+        <v>0.0009428625306430324</v>
       </c>
     </row>
     <row r="810">
@@ -15007,7 +15007,7 @@
         <v>5</v>
       </c>
       <c r="D814">
-        <v>0.0009428625306430323</v>
+        <v>0.0009428625306430324</v>
       </c>
     </row>
     <row r="815">
@@ -15025,7 +15025,7 @@
         <v>5</v>
       </c>
       <c r="D815">
-        <v>0.0009428625306430323</v>
+        <v>0.0009428625306430324</v>
       </c>
     </row>
     <row r="816">
@@ -15133,7 +15133,7 @@
         <v>5</v>
       </c>
       <c r="D821">
-        <v>0.0009428625306430323</v>
+        <v>0.0009428625306430324</v>
       </c>
     </row>
     <row r="822">
@@ -15241,7 +15241,7 @@
         <v>5</v>
       </c>
       <c r="D827">
-        <v>0.0009428625306430323</v>
+        <v>0.0009428625306430324</v>
       </c>
     </row>
     <row r="828">
@@ -15637,7 +15637,7 @@
         <v>5</v>
       </c>
       <c r="D849">
-        <v>0.0009428625306430323</v>
+        <v>0.0009428625306430324</v>
       </c>
     </row>
     <row r="850">
@@ -16015,7 +16015,7 @@
         <v>5</v>
       </c>
       <c r="D870">
-        <v>0.0009428625306430323</v>
+        <v>0.0009428625306430324</v>
       </c>
     </row>
     <row r="871">
@@ -16519,7 +16519,7 @@
         <v>5</v>
       </c>
       <c r="D898">
-        <v>0.0009428625306430323</v>
+        <v>0.0009428625306430324</v>
       </c>
     </row>
     <row r="899">
@@ -17419,7 +17419,7 @@
         <v>5</v>
       </c>
       <c r="D948">
-        <v>0.0009428625306430323</v>
+        <v>0.0009428625306430324</v>
       </c>
     </row>
     <row r="949">
@@ -17761,7 +17761,7 @@
         <v>5</v>
       </c>
       <c r="D967">
-        <v>0.0009428625306430323</v>
+        <v>0.0009428625306430324</v>
       </c>
     </row>
     <row r="968">
@@ -17887,7 +17887,7 @@
         <v>5</v>
       </c>
       <c r="D974">
-        <v>0.0009428625306430323</v>
+        <v>0.0009428625306430324</v>
       </c>
     </row>
     <row r="975">
@@ -17905,7 +17905,7 @@
         <v>5</v>
       </c>
       <c r="D975">
-        <v>0.0009428625306430323</v>
+        <v>0.0009428625306430324</v>
       </c>
     </row>
     <row r="976">
@@ -18103,7 +18103,7 @@
         <v>5</v>
       </c>
       <c r="D986">
-        <v>0.0009428625306430323</v>
+        <v>0.0009428625306430324</v>
       </c>
     </row>
     <row r="987">
@@ -18391,7 +18391,7 @@
         <v>5</v>
       </c>
       <c r="D1002">
-        <v>0.0009428625306430323</v>
+        <v>0.0009428625306430324</v>
       </c>
     </row>
     <row r="1003">
@@ -18877,7 +18877,7 @@
         <v>5</v>
       </c>
       <c r="D1029">
-        <v>0.0009428625306430323</v>
+        <v>0.0009428625306430324</v>
       </c>
     </row>
     <row r="1030">
@@ -19111,7 +19111,7 @@
         <v>5</v>
       </c>
       <c r="D1042">
-        <v>0.0009428625306430323</v>
+        <v>0.0009428625306430324</v>
       </c>
     </row>
     <row r="1043">
